--- a/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
+++ b/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/kondrashov/Outputs_primates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="1240" windowWidth="11920" windowHeight="17100" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1077,17 +1078,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" style="1"/>
-    <col min="2" max="2" width="18.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.19921875" style="1"/>
+    <col min="2" max="2" width="18.796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.1640625" style="1"/>
-    <col min="10" max="10" width="55.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.1640625" style="1"/>
+    <col min="4" max="9" width="11.19921875" style="1"/>
+    <col min="10" max="10" width="55.296875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.19921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1119,7 +1120,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1146,7 +1147,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1172,7 +1173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1198,7 +1199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1224,7 +1225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>190</v>
       </c>
@@ -1250,7 +1251,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1302,7 +1303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,7 +1329,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1432,7 +1433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1510,7 +1511,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1536,7 +1537,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
@@ -1565,7 +1566,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1591,7 +1592,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
@@ -1643,7 +1644,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
@@ -1669,7 +1670,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>63</v>
       </c>
@@ -1695,7 +1696,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -1721,7 +1722,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1747,7 +1748,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>73</v>
       </c>
@@ -1799,7 +1800,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>76</v>
       </c>
@@ -1825,7 +1826,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>78</v>
       </c>
@@ -1851,7 +1852,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>78</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>81</v>
       </c>
@@ -1903,7 +1904,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>83</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>83</v>
       </c>
@@ -1952,7 +1953,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>85</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>88</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>88</v>
       </c>
@@ -2039,7 +2040,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>88</v>
       </c>
@@ -2117,7 +2118,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>88</v>
       </c>
@@ -2143,7 +2144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>88</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>88</v>
       </c>
@@ -2195,7 +2196,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>88</v>
       </c>
@@ -2221,7 +2222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>90</v>
       </c>
@@ -2247,7 +2248,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>93</v>
       </c>
@@ -2273,7 +2274,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>95</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>97</v>
       </c>
@@ -2325,7 +2326,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>100</v>
       </c>
@@ -2354,7 +2355,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
@@ -2380,7 +2381,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>105</v>
       </c>
@@ -2406,7 +2407,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>105</v>
       </c>
@@ -2432,7 +2433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>108</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>110</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>110</v>
       </c>
@@ -2510,7 +2511,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>110</v>
       </c>
@@ -2536,7 +2537,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2562,7 +2563,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>113</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>116</v>
       </c>
@@ -2614,7 +2615,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>118</v>
       </c>
@@ -2640,7 +2641,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>121</v>
       </c>
@@ -2666,7 +2667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>123</v>
       </c>
@@ -2692,7 +2693,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>126</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>129</v>
       </c>
@@ -2744,7 +2745,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>132</v>
       </c>
@@ -2770,7 +2771,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>132</v>
       </c>
@@ -2796,7 +2797,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>132</v>
       </c>
@@ -2822,7 +2823,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>132</v>
       </c>
@@ -2848,7 +2849,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2874,7 +2875,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>134</v>
       </c>
@@ -2900,7 +2901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>136</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>

--- a/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
+++ b/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3967BC57-CF2F-43EA-8845-48F33818D889}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1161,7 +1160,7 @@
         <v>31</v>
       </c>
       <c r="E3" s="1">
-        <v>1119</v>
+        <v>119</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>

--- a/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
+++ b/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3967BC57-CF2F-43EA-8845-48F33818D889}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A60B7D-65F6-42C0-8389-BEBA518C90BD}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="201">
   <si>
     <t>gene</t>
   </si>
@@ -639,13 +639,16 @@
   </si>
   <si>
     <t>variable_amino_acids</t>
+  </si>
+  <si>
+    <t>This is NOT A VALID CPD!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -678,6 +681,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -728,7 +738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -742,6 +752,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1617,30 +1628,33 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="11">
         <v>13</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="11">
         <v>128</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="11" t="s">
         <v>60</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">

--- a/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
+++ b/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A60B7D-65F6-42C0-8389-BEBA518C90BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACFD2B4-1B40-914D-83F3-38793A614317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="34320" yWindow="16460" windowWidth="15980" windowHeight="12340" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="204">
   <si>
     <t>gene</t>
   </si>
@@ -642,13 +642,22 @@
   </si>
   <si>
     <t>This is NOT A VALID CPD!</t>
+  </si>
+  <si>
+    <t>at Human site 309? NOT vALID!</t>
+  </si>
+  <si>
+    <t>NOT Valid score is 55</t>
+  </si>
+  <si>
+    <t>NOT VALID score is -15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -686,6 +695,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -738,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -752,7 +768,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1088,17 +1106,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" style="1"/>
-    <col min="2" max="2" width="18.796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" style="1"/>
+    <col min="2" max="2" width="18.83203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
-    <col min="4" max="9" width="11.19921875" style="1"/>
-    <col min="10" max="10" width="55.296875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.19921875" style="1"/>
+    <col min="4" max="9" width="11.1640625" style="1"/>
+    <col min="10" max="10" width="55.33203125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1148,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1157,7 +1175,7 @@
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1183,7 +1201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1209,7 +1227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1235,7 +1253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>190</v>
       </c>
@@ -1261,7 +1279,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1287,7 +1305,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1313,7 +1331,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -1339,7 +1357,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1365,7 +1383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1391,33 +1409,33 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="11">
         <v>1459</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="11">
         <v>2851</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1443,33 +1461,33 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="11">
         <v>93</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="11">
         <v>155</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="11" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -1495,7 +1513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1521,7 +1539,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1547,7 +1565,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
@@ -1576,7 +1594,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1602,7 +1620,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>55</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>58</v>
       </c>
@@ -1657,7 +1675,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>61</v>
       </c>
@@ -1683,33 +1701,36 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="11">
         <v>296</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="11">
         <v>298</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="11" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I23" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>66</v>
       </c>
@@ -1735,7 +1756,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1761,7 +1782,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>66</v>
       </c>
@@ -1787,33 +1808,33 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="11">
         <v>1042</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="11">
         <v>1056</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>76</v>
       </c>
@@ -1839,7 +1860,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>78</v>
       </c>
@@ -1865,7 +1886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>78</v>
       </c>
@@ -1891,7 +1912,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>81</v>
       </c>
@@ -1917,30 +1938,30 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="12">
         <v>318</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>83</v>
       </c>
@@ -1966,7 +1987,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>85</v>
       </c>
@@ -1998,7 +2019,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>88</v>
       </c>
@@ -2027,33 +2048,36 @@
         <v>187</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="13">
         <v>535</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="13">
         <v>539</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>88</v>
       </c>
@@ -2079,7 +2103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
@@ -2105,7 +2129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>88</v>
       </c>
@@ -2131,7 +2155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>88</v>
       </c>
@@ -2157,7 +2181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>88</v>
       </c>
@@ -2183,7 +2207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>88</v>
       </c>
@@ -2209,7 +2233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>88</v>
       </c>
@@ -2235,7 +2259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>90</v>
       </c>
@@ -2261,7 +2285,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>93</v>
       </c>
@@ -2287,7 +2311,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>95</v>
       </c>
@@ -2313,33 +2337,33 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="11">
         <v>114</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="11">
         <v>307</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>100</v>
       </c>
@@ -2368,7 +2392,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
@@ -2394,7 +2418,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>105</v>
       </c>
@@ -2420,7 +2444,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>105</v>
       </c>
@@ -2446,7 +2470,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>108</v>
       </c>
@@ -2472,7 +2496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>110</v>
       </c>
@@ -2498,7 +2522,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>110</v>
       </c>
@@ -2524,7 +2548,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>110</v>
       </c>
@@ -2550,7 +2574,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
@@ -2576,33 +2600,36 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="1" t="s">
+    <row r="57" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="11">
         <v>1</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="11">
         <v>83</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="11" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>116</v>
       </c>
@@ -2628,7 +2655,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>118</v>
       </c>
@@ -2654,7 +2681,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>121</v>
       </c>
@@ -2680,7 +2707,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>123</v>
       </c>
@@ -2706,7 +2733,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>126</v>
       </c>
@@ -2732,7 +2759,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>129</v>
       </c>
@@ -2758,7 +2785,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>132</v>
       </c>
@@ -2784,7 +2811,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>132</v>
       </c>
@@ -2810,7 +2837,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>132</v>
       </c>
@@ -2836,7 +2863,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>132</v>
       </c>
@@ -2862,7 +2889,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>132</v>
       </c>
@@ -2888,7 +2915,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>134</v>
       </c>
@@ -2914,7 +2941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="10" t="s">
         <v>136</v>
       </c>
@@ -2943,7 +2970,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>138</v>
       </c>

--- a/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
+++ b/Outputs_primates/AllGenes_CPDs_confirmed.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{09B33106-9024-5942-8387-42FED146F2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65A60B7D-65F6-42C0-8389-BEBA518C90BD}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="14940" yWindow="0" windowWidth="8196" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -752,7 +752,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
